--- a/preview/pr-13/CodeSystem-dem-erwerbsstatus.xlsx
+++ b/preview/pr-13/CodeSystem-dem-erwerbsstatus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T07:34:58+00:00</t>
+    <t>2026-09-30T07:33:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -141,67 +141,67 @@
     <t>selbststaendig</t>
   </si>
   <si>
-    <t>Selbstständigerwerbend</t>
+    <t>Self-employed [work for yourself]</t>
   </si>
   <si>
     <t>angestellt</t>
   </si>
   <si>
-    <t>Angestellt</t>
+    <t>In paid employment [work for someone else]</t>
   </si>
   <si>
     <t>arbeitssuchend</t>
   </si>
   <si>
-    <t>Arbeitssuchend</t>
+    <t>Looking for work</t>
   </si>
   <si>
     <t>haushalt</t>
   </si>
   <si>
-    <t>Hausfrau/Hausmann</t>
+    <t>Looking after the home</t>
   </si>
   <si>
     <t>arbeitsunfaehig</t>
   </si>
   <si>
-    <t>Krankheitsbedingte Arbeitsunfähigkeit</t>
+    <t>Unable to work due to sickness or ill-health</t>
   </si>
   <si>
     <t>pensioniert</t>
   </si>
   <si>
-    <t>Pensioniert</t>
+    <t>Retired</t>
   </si>
   <si>
     <t>student</t>
   </si>
   <si>
-    <t>Student/in</t>
+    <t>Student</t>
   </si>
   <si>
     <t>nicht-arbeitend</t>
   </si>
   <si>
-    <t>Nicht arbeitend und nicht arbeitssuchend</t>
+    <t>Not working and not looking for work</t>
   </si>
   <si>
     <t>lernende</t>
   </si>
   <si>
-    <t>Lernende/r</t>
+    <t>Apprentice</t>
   </si>
   <si>
     <t>anderes</t>
   </si>
   <si>
-    <t>Anderes</t>
+    <t>Other</t>
   </si>
   <si>
     <t>weiss-nicht</t>
   </si>
   <si>
-    <t>Ich weiss es nicht</t>
+    <t>Don't know</t>
   </si>
 </sst>
 </file>

--- a/preview/pr-13/CodeSystem-dem-erwerbsstatus.xlsx
+++ b/preview/pr-13/CodeSystem-dem-erwerbsstatus.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T07:33:31+00:00</t>
+    <t>2026-09-30T08:17:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/preview/pr-13/CodeSystem-dem-erwerbsstatus.xlsx
+++ b/preview/pr-13/CodeSystem-dem-erwerbsstatus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T08:17:00+00:00</t>
+    <t>2026-09-30T08:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
